--- a/data/inversiones/ahorro.xlsx
+++ b/data/inversiones/ahorro.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Adrian\Bots\FinancialAgent\data\inversiones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codigos\FinancialAgent\data\inversiones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E086E924-DB91-4E80-A85A-B146778286A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE6506B-D851-49D2-B0DB-A43AB9CF024F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cuentas de Ahorro" sheetId="1" r:id="rId1"/>
@@ -402,12 +402,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -435,13 +435,13 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>10297.16</v>
+        <v>8753.5</v>
       </c>
       <c r="E2">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -452,13 +452,13 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>2443.8200000000002</v>
+        <v>6149.7</v>
       </c>
       <c r="E3">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -469,7 +469,7 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>200.9</v>
+        <v>251.11</v>
       </c>
       <c r="E4">
         <v>13</v>
